--- a/productos/03-control-deudas/Control-de-Deudas.xlsx
+++ b/productos/03-control-deudas/Control-de-Deudas.xlsx
@@ -123,7 +123,7 @@
     <t xml:space="preserve">7. Celdas protegidas</t>
   </si>
   <si>
-    <t xml:space="preserve">Las hojas están protegidas para que no borres fórmulas por accidente. Solo puedes escribir en las celdas resaltadas en color crema / texto azul. Contraseña de desprotección: plantilla2026.</t>
+    <t xml:space="preserve">Las hojas están protegidas para que no borres fórmulas por accidente. Solo puedes escribir en las celdas resaltadas en color crema / texto azul. Si necesitas editar otra celda, ve a Revisar → Desproteger hoja (no pide contraseña).</t>
   </si>
   <si>
     <t xml:space="preserve">Soporte y otras plantillas de esta línea de productos: www.tumarca.com</t>
@@ -1727,11 +1727,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="35049379"/>
-        <c:axId val="32410016"/>
+        <c:axId val="71659956"/>
+        <c:axId val="48743817"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="35049379"/>
+        <c:axId val="71659956"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1763,7 +1763,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="32410016"/>
+        <c:crossAx val="48743817"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1771,7 +1771,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="32410016"/>
+        <c:axId val="48743817"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1813,7 +1813,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="35049379"/>
+        <c:crossAx val="71659956"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2061,11 +2061,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="26988629"/>
-        <c:axId val="53138466"/>
+        <c:axId val="3156710"/>
+        <c:axId val="78889849"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="26988629"/>
+        <c:axId val="3156710"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2097,7 +2097,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="53138466"/>
+        <c:crossAx val="78889849"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2105,7 +2105,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="53138466"/>
+        <c:axId val="78889849"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2147,7 +2147,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="26988629"/>
+        <c:crossAx val="3156710"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2649,7 +2649,7 @@
       <c r="F24" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="true" password="ee36" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
+  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
   <mergeCells count="16">
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="B4:F6"/>
@@ -2788,7 +2788,7 @@
       <c r="C25" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="true" password="ee36" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
+  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
   <mergeCells count="16">
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B4:C4"/>
@@ -2944,7 +2944,7 @@
       <c r="D14" s="20"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="true" password="ee36" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
+  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
   <mergeCells count="2">
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B14:D14"/>
@@ -3399,7 +3399,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection sheet="true" password="ee36" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
+  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
   <mergeCells count="2">
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A3:J3"/>
@@ -5594,7 +5594,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection sheet="true" password="ee36" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
+  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A3:E3"/>
@@ -6133,7 +6133,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection sheet="true" password="ee36" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
+  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
   <mergeCells count="4">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="B3:G3"/>
@@ -6237,7 +6237,7 @@
       <c r="I7" s="43"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="true" password="ee36" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
+  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
   <mergeCells count="10">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
